--- a/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.2-beef-enteric/3.2-beef-enteric.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/3.2-beef-enteric/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F2BE2B-1630-E84F-AF43-2F82CFE88775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F041B89-0D77-F64E-8395-031D4EEB916D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.2.1 methane" sheetId="1" r:id="rId1"/>
@@ -19,6 +14,9 @@
     <sheet name="3.2.1" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="3" hidden="1">'3.2.1'!$X$23:$AN$63</definedName>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">Table1!$A$1:$M$58</definedName>
@@ -1943,6 +1941,31 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="2" xr16:uid="{25076068-96F8-6642-A28E-844BBFD23961}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="14">
@@ -2021,9 +2044,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{420EF3BD-8869-564A-AC30-3CFBDA0735BD}" name="Table1" displayName="Table1" ref="A1:M58" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:M58" xr:uid="{420EF3BD-8869-564A-AC30-3CFBDA0735BD}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{8046ABC1-ECBF-B445-80AE-4B9EE134EB2D}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D5B02C07-4A90-C14B-9FC6-52E5398E7E46}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{05C830C2-1868-794F-8615-24A6D55DBC7E}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{8046ABC1-ECBF-B445-80AE-4B9EE134EB2D}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D5B02C07-4A90-C14B-9FC6-52E5398E7E46}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{05C830C2-1868-794F-8615-24A6D55DBC7E}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{7B3E2470-714D-A247-B223-2A71F85E4D96}" uniqueName="4" name="Column4" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2184AD9E-4C8D-2342-A95B-6B9533492777}" uniqueName="5" name="Column5" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{1DC9398D-7E62-1D4C-8F6A-E600C76A1655}" uniqueName="6" name="Column6" queryTableFieldId="6"/>
@@ -2111,8 +2134,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1DB3466D-5B19-2F42-AD2B-57D5F103527C}" name="TableLWG" displayName="TableLWG" ref="X23:AN63" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="X23:AN63" xr:uid="{1DB3466D-5B19-2F42-AD2B-57D5F103527C}"/>
   <tableColumns count="17">
-    <tableColumn id="2" xr3:uid="{9DBFF1DA-DC38-A141-85CC-ECBF8B2B62C1}" uniqueName="2" name="Season" queryTableFieldId="2" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{4D533652-5013-DE4D-B610-57C54A69E4E3}" uniqueName="3" name="Class" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{9DBFF1DA-DC38-A141-85CC-ECBF8B2B62C1}" uniqueName="2" name="Season" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{4D533652-5013-DE4D-B610-57C54A69E4E3}" uniqueName="3" name="Class" queryTableFieldId="3" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{9CD989C1-3306-F544-997B-8438ECA8579C}" uniqueName="4" name="ACT/NSW" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{294F0417-AE13-804C-9E7E-E3F1BBA4867A}" uniqueName="5" name="SA" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{B56ADC37-291D-C641-AFA5-9E3AE815A5AF}" uniqueName="6" name="TAS" queryTableFieldId="6"/>
@@ -2848,8 +2871,8 @@
         <v>50</v>
       </c>
       <c r="CD7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8" spans="1:92" x14ac:dyDescent="0.2">
@@ -3293,7 +3316,7 @@
       </c>
       <c r="AZ11">
         <f>$CD$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BA11">
         <f>$CD$8</f>
@@ -7896,7 +7919,7 @@
       </c>
       <c r="AZ51">
         <f>$CD$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BA51">
         <f>$CD$8</f>
@@ -13012,7 +13035,7 @@
       </c>
       <c r="AZ91">
         <f>$CD$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BA91">
         <f>$CD$8</f>
@@ -18337,7 +18360,7 @@
       </c>
       <c r="AZ141">
         <f>$CD$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BA141">
         <f>$CD$8</f>
@@ -23394,7 +23417,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A4:CP11 A123:CP123 A120:M122 P120:AL122 A115:CP115 A112:M114 AO112:CP114 A131:CP157 A128:M130 P128:AL130 A119:CP119 A116:M118 P116:AL118 A111:CP111 A108:M110 P108:AL110 A103:CP103 A100:M102 AO100:CP102 A127:CP127 A124:M126 P124:AL126 AO108:CP110 A107:CP107 A104:M106 P104:AL106 AO116:CP118 AO128:CP130 AO104:CP106 P112:AL114 AO124:CP126 A161:CP180 A158:N160 P158:CP160 AO120:CP122 A99:CP99 A96:M98 AO96:CP98 P100:AL102 A79:CP79 A76:M78 P76:AL78 A71:CP71 A68:M70 P68:AL70 A67:CP67 A64:M66 AO64:CP66 A83:CP83 A80:M82 AO80:CP82 AO68:CP70 A51:CP51 A48:M50 AO48:CP50 P48:AL50 A95:CP95 A92:M94 P92:AL94 AO76:CP78 A59:CP59 A56:M58 P56:AL58 A55:CP55 A52:M54 P52:AL54 AO92:CP94 A91:CP91 A88:M90 P88:AL90 A75:CP75 A72:M74 AO72:CP74 A87:CP87 A84:M86 P84:AL86 AO84:CP86 A39:CP39 A36:M38 AO36:CP38 P80:AL82 AO52:CP54 A43:CP43 A40:M42 AO40:CP42 P40:AL42 A27:CP27 A24:M26 P24:AL26 AO88:CP90 A63:CP63 A60:M62 AO60:CP62 A35:CP35 A32:M34 AO32:CP34 A47:CP47 A44:M46 P44:AL46 P64:AL66 P96:AL98 AO44:CP46 A19:CP19 A16:M18 P16:AL18 AO56:CP58 P36:AL38 A31:CP31 A28:M30 P28:AL30 P72:AL74 AO28:CP30 A23:CP23 A20:M22 P20:AL22 A15:CP15 A12:M14 P12:AL14 P60:AL62 P32:AL34 AO24:CP26 AO16:CP18 AO12:CP14 AO20:CP22" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:CP6 A123:CP123 A120:M122 P120:AL122 A115:CP115 A112:M114 AO112:CP114 A131:CP157 A128:M130 P128:AL130 A119:CP119 A116:M118 P116:AL118 A111:CP111 A108:M110 P108:AL110 A103:CP103 A100:M102 AO100:CP102 A127:CP127 A124:M126 P124:AL126 AO108:CP110 A107:CP107 A104:M106 P104:AL106 AO116:CP118 AO128:CP130 AO104:CP106 P112:AL114 AO124:CP126 A161:CP180 A158:N160 P158:CP160 AO120:CP122 A99:CP99 A96:M98 AO96:CP98 P100:AL102 A79:CP79 A76:M78 P76:AL78 A71:CP71 A68:M70 P68:AL70 A67:CP67 A64:M66 AO64:CP66 A83:CP83 A80:M82 AO80:CP82 AO68:CP70 A51:CP51 A48:M50 AO48:CP50 P48:AL50 A95:CP95 A92:M94 P92:AL94 AO76:CP78 A59:CP59 A56:M58 P56:AL58 A55:CP55 A52:M54 P52:AL54 AO92:CP94 A91:CP91 A88:M90 P88:AL90 A75:CP75 A72:M74 AO72:CP74 A87:CP87 A84:M86 P84:AL86 AO84:CP86 A39:CP39 A36:M38 AO36:CP38 P80:AL82 AO52:CP54 A43:CP43 A40:M42 AO40:CP42 P40:AL42 A27:CP27 A24:M26 P24:AL26 AO88:CP90 A63:CP63 A60:M62 AO60:CP62 A35:CP35 A32:M34 AO32:CP34 A47:CP47 A44:M46 P44:AL46 P64:AL66 P96:AL98 AO44:CP46 A19:CP19 A16:M18 P16:AL18 AO56:CP58 P36:AL38 A31:CP31 A28:M30 P28:AL30 P72:AL74 AO28:CP30 A23:CP23 A20:M22 P20:AL22 A15:CP15 A12:M14 P12:AL14 P60:AL62 P32:AL34 AO24:CP26 AO16:CP18 AO12:CP14 AO20:CP22 A8:CP11 A7:CC7 CE7:CP7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
